--- a/artfynd/A 29797-2025 artfynd.xlsx
+++ b/artfynd/A 29797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121476923</v>
+        <v>121476746</v>
       </c>
       <c r="B2" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587354</v>
+        <v>587191</v>
       </c>
       <c r="R2" t="n">
-        <v>7273677</v>
+        <v>7274086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,50 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121476469</v>
+        <v>121532194</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587097</v>
+        <v>587190</v>
       </c>
       <c r="R3" t="n">
-        <v>7274144</v>
+        <v>7274086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>03:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +871,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121476468</v>
+        <v>121476923</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>587446</v>
+        <v>587354</v>
       </c>
       <c r="R4" t="n">
-        <v>7273737</v>
+        <v>7273677</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,50 +980,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121477292</v>
+        <v>121532708</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jiltjaurberget, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>587354</v>
       </c>
       <c r="R5" t="n">
-        <v>7273677</v>
+        <v>7273676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1049,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-01-15</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-01-17</t>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,49 +1079,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isak Sarac</t>
+          <t>Max Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121476746</v>
+        <v>121476585</v>
       </c>
       <c r="B6" t="n">
-        <v>77957</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587191</v>
+        <v>586919</v>
       </c>
       <c r="R6" t="n">
-        <v>7274086</v>
+        <v>7274217</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1188,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121532194</v>
+        <v>121532432</v>
       </c>
       <c r="B7" t="n">
-        <v>77957</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>498</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1229,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587190</v>
+        <v>586918</v>
       </c>
       <c r="R7" t="n">
-        <v>7274086</v>
+        <v>7274216</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1264,7 +1262,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1274,7 +1272,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,19 +1299,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121533091</v>
+        <v>121477292</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1334,21 +1327,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>587354</v>
       </c>
       <c r="R8" t="n">
-        <v>7273676</v>
+        <v>7273677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1375,22 +1364,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,49 +1384,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Max Jonsson</t>
+          <t>Isak Sarac</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121532708</v>
+        <v>121533091</v>
       </c>
       <c r="B9" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,7 +1470,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1506,7 +1480,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,15 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121532350</v>
+        <v>121476468</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,18 +1535,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Jiltjaurberget, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>587445</v>
+        <v>587446</v>
       </c>
       <c r="R10" t="n">
         <v>7273737</v>
@@ -1607,22 +1572,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>02:00</t>
+          <t>2020-01-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-05-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>02:00</t>
+          <t>2020-01-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,15 +1592,465 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121476469</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Jiltjaurberget, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>587097</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7274144</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-01-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Sarac</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121532350</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>587445</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7273737</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Max Jonsson</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Max Jonsson</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>96498652</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Jiljaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>587295</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7273953</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-07</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Emelie Walden</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Emelie Walden, Johan Eklöf, Emelie Waldén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>96498668</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn och tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Jiljaur, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>587288</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7273744</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>21:39</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emelie Walden</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emelie Walden, Johan Eklöf, Emelie Waldén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29797-2025 artfynd.xlsx
+++ b/artfynd/A 29797-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121476746</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121532194</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121476923</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121532708</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,6 +1210,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121476585</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121532432</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121477292</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121533091</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121476468</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121476469</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121532350</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1930,6 +1990,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96498652</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2051,8 +2116,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96498668</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>